--- a/data/trans_orig/P5_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P5_R-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17345</t>
+          <t>17443</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29090</t>
+          <t>29521</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>52,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16437</t>
+          <t>15636</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27483</t>
+          <t>27051</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>52,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>36431</t>
+          <t>36673</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>52702</t>
+          <t>52352</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>48,55%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27372</t>
+          <t>26941</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>39117</t>
+          <t>39019</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>48,48%</t>
+          <t>47,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>69,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23888</t>
+          <t>24320</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34934</t>
+          <t>35735</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>47,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,0%</t>
+          <t>69,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>55131</t>
+          <t>55481</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>71402</t>
+          <t>71160</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>51,13%</t>
+          <t>51,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>66,22%</t>
+          <t>65,99%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>69307</t>
+          <t>69786</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>93989</t>
+          <t>95326</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>82141</t>
+          <t>82470</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>107890</t>
+          <t>109319</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>158862</t>
+          <t>157440</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>196106</t>
+          <t>194637</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,31%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>216328</t>
+          <t>214991</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>241010</t>
+          <t>240531</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69,71%</t>
+          <t>69,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,67%</t>
+          <t>77,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>245746</t>
+          <t>244317</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>271495</t>
+          <t>271166</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,49%</t>
+          <t>69,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>76,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>467847</t>
+          <t>469316</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>505091</t>
+          <t>506513</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>70,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>76,29%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29457</t>
+          <t>28679</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>45857</t>
+          <t>45811</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23859</t>
+          <t>23883</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39851</t>
+          <t>39450</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>56735</t>
+          <t>56945</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>78934</t>
+          <t>80904</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>31,1%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>90724</t>
+          <t>90770</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>107124</t>
+          <t>107902</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>66,43%</t>
+          <t>66,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,43%</t>
+          <t>79,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>83691</t>
+          <t>84092</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>99683</t>
+          <t>99659</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,74%</t>
+          <t>68,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>80,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>181189</t>
+          <t>179219</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>203388</t>
+          <t>203178</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>69,66%</t>
+          <t>68,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>78,11%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>125887</t>
+          <t>124435</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>158034</t>
+          <t>156383</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>130804</t>
+          <t>132896</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>162956</t>
+          <t>166042</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>264926</t>
+          <t>265693</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>311705</t>
+          <t>313158</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,35%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>345325</t>
+          <t>346976</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>377472</t>
+          <t>378924</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,6%</t>
+          <t>68,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,99%</t>
+          <t>75,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>365593</t>
+          <t>362507</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>397745</t>
+          <t>395653</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>68,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>74,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>720203</t>
+          <t>718750</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>766982</t>
+          <t>766215</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,33%</t>
+          <t>74,25%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13327</t>
+          <t>13551</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24918</t>
+          <t>25599</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,91%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16416</t>
+          <t>16623</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29153</t>
+          <t>28903</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>46,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33574</t>
+          <t>34256</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49471</t>
+          <t>50149</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,08%</t>
+          <t>42,65%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30566</t>
+          <t>29885</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42157</t>
+          <t>41933</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>53,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>75,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>32937</t>
+          <t>33187</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>45674</t>
+          <t>45467</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>53,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>73,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>68103</t>
+          <t>67425</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>84000</t>
+          <t>83318</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>57,92%</t>
+          <t>57,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,44%</t>
+          <t>70,86%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>101303</t>
+          <t>101869</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>129861</t>
+          <t>128818</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,63%</t>
+          <t>42,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>111657</t>
+          <t>111868</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>140235</t>
+          <t>141566</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>41,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>222206</t>
+          <t>221254</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>263659</t>
+          <t>259726</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>40,3%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>174792</t>
+          <t>175835</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>203350</t>
+          <t>202784</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>57,37%</t>
+          <t>57,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>66,75%</t>
+          <t>66,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>199558</t>
+          <t>198227</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>228136</t>
+          <t>227925</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,73%</t>
+          <t>58,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>67,14%</t>
+          <t>67,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>380787</t>
+          <t>384720</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>422240</t>
+          <t>423192</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,09%</t>
+          <t>59,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,52%</t>
+          <t>65,67%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>38442</t>
+          <t>38085</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>55868</t>
+          <t>55448</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>47,82%</t>
+          <t>47,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>48277</t>
+          <t>46724</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>67388</t>
+          <t>66757</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>49,23%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>90870</t>
+          <t>92287</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>117310</t>
+          <t>118275</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>36,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,24%</t>
+          <t>46,62%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>60959</t>
+          <t>61379</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>78385</t>
+          <t>78742</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>52,18%</t>
+          <t>52,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>67,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>69510</t>
+          <t>70141</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>88621</t>
+          <t>90174</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>51,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,74%</t>
+          <t>65,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>136415</t>
+          <t>135450</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>162855</t>
+          <t>161438</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>53,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>64,19%</t>
+          <t>63,63%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>165150</t>
+          <t>164635</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>199619</t>
+          <t>199800</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>41,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>186550</t>
+          <t>189494</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>224109</t>
+          <t>224900</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>362249</t>
+          <t>360875</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>412672</t>
+          <t>412380</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>40,6%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>277346</t>
+          <t>277165</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>311815</t>
+          <t>312330</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>58,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>314672</t>
+          <t>313881</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>352231</t>
+          <t>349287</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,4%</t>
+          <t>58,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>64,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>603074</t>
+          <t>603366</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>653497</t>
+          <t>654871</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,37%</t>
+          <t>59,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>64,47%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8159</t>
+          <t>8343</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17247</t>
+          <t>17183</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>42,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15524</t>
+          <t>15513</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26806</t>
+          <t>27249</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>53,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25608</t>
+          <t>26764</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>40701</t>
+          <t>40797</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,3%</t>
+          <t>44,4%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23394</t>
+          <t>23458</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>32482</t>
+          <t>32298</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
+          <t>57,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,92%</t>
+          <t>79,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24431</t>
+          <t>23988</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>35713</t>
+          <t>35724</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>46,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,7%</t>
+          <t>69,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>51177</t>
+          <t>51081</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>66270</t>
+          <t>65114</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>55,7%</t>
+          <t>55,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>72,13%</t>
+          <t>70,87%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>104361</t>
+          <t>104818</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>133374</t>
+          <t>134055</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>117858</t>
+          <t>118404</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>148081</t>
+          <t>147544</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>232919</t>
+          <t>229369</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>273263</t>
+          <t>270805</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>37,23%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>214181</t>
+          <t>213500</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>243194</t>
+          <t>242737</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>61,63%</t>
+          <t>61,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,97%</t>
+          <t>69,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>231785</t>
+          <t>232322</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>262008</t>
+          <t>261462</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,02%</t>
+          <t>61,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,97%</t>
+          <t>68,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>454158</t>
+          <t>456616</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>494502</t>
+          <t>498052</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,43%</t>
+          <t>62,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>68,47%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>43553</t>
+          <t>43396</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>62253</t>
+          <t>61433</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>45,77%</t>
+          <t>45,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>50996</t>
+          <t>49483</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>69945</t>
+          <t>68632</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>49,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>97211</t>
+          <t>98131</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>124066</t>
+          <t>125227</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>45,38%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>73774</t>
+          <t>74594</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>92474</t>
+          <t>92631</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>54,23%</t>
+          <t>54,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>68,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>69985</t>
+          <t>71298</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>88934</t>
+          <t>90447</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>50,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>63,56%</t>
+          <t>64,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>151891</t>
+          <t>150730</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>178746</t>
+          <t>177826</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
+          <t>54,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>64,77%</t>
+          <t>64,44%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>166203</t>
+          <t>166664</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>201377</t>
+          <t>201612</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>38,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>193596</t>
+          <t>196243</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>231374</t>
+          <t>232148</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>40,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>369934</t>
+          <t>371768</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>423452</t>
+          <t>424218</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>38,73%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>322846</t>
+          <t>322611</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>358020</t>
+          <t>357559</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,59%</t>
+          <t>61,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,3%</t>
+          <t>68,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>339659</t>
+          <t>338885</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>377437</t>
+          <t>374790</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>59,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>65,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>671804</t>
+          <t>671038</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>725322</t>
+          <t>723488</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>61,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,22%</t>
+          <t>66,06%</t>
         </is>
       </c>
     </row>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3874</t>
+          <t>3798</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12969</t>
+          <t>13140</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9212</t>
+          <t>9383</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22153</t>
+          <t>21389</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15823</t>
+          <t>15538</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32711</t>
+          <t>31007</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>26,57%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>41709</t>
+          <t>41538</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>50804</t>
+          <t>50880</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,28%</t>
+          <t>75,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39851</t>
+          <t>40615</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>52792</t>
+          <t>52621</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>64,27%</t>
+          <t>65,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>83971</t>
+          <t>85675</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>100859</t>
+          <t>101144</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,97%</t>
+          <t>73,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>86,68%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>77054</t>
+          <t>76840</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>180260</t>
+          <t>178132</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>65541</t>
+          <t>66551</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>97172</t>
+          <t>96974</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>154557</t>
+          <t>155181</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>266577</t>
+          <t>265359</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,16%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>280250</t>
+          <t>282378</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>383456</t>
+          <t>383670</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>60,86%</t>
+          <t>61,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>83,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>419447</t>
+          <t>419645</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>451078</t>
+          <t>450068</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>81,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>710552</t>
+          <t>711770</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>822572</t>
+          <t>821948</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,72%</t>
+          <t>72,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,18%</t>
+          <t>84,12%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22972</t>
+          <t>22823</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38605</t>
+          <t>39053</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25629</t>
+          <t>25239</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44246</t>
+          <t>44383</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>52369</t>
+          <t>50942</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>77764</t>
+          <t>77171</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,25%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>110946</t>
+          <t>110498</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>126579</t>
+          <t>126728</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>73,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,64%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>138159</t>
+          <t>138022</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>156776</t>
+          <t>157166</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,74%</t>
+          <t>75,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,95%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>254193</t>
+          <t>254786</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>279588</t>
+          <t>281015</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,57%</t>
+          <t>76,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>84,65%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>113404</t>
+          <t>111726</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>205224</t>
+          <t>213673</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>111905</t>
+          <t>110621</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>149274</t>
+          <t>151459</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>239320</t>
+          <t>237586</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>348796</t>
+          <t>342996</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,06%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>459514</t>
+          <t>451065</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>551334</t>
+          <t>553012</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,13%</t>
+          <t>67,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>83,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>611754</t>
+          <t>609569</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>649123</t>
+          <t>650407</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>80,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>85,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1076971</t>
+          <t>1082771</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1186447</t>
+          <t>1188181</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,54%</t>
+          <t>75,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>83,34%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P5_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P5_R-Estudios-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>21644</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>15890</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>27453</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>42,13%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>30,93%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>53,44%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>23180</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>17443</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>29521</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>17714</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>29391</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>41,05%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>30,89%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>52,28%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>21644</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>15636</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>27051</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>42,13%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>52,66%</t>
+          <t>52,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>36673</t>
+          <t>36397</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>52352</t>
+          <t>53764</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>49,86%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>29727</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>23918</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>35481</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>57,87%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>46,56%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>69,07%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>33282</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>26941</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>39019</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>27071</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>38748</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>58,95%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>47,72%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>69,11%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>29727</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>24320</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>35735</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>57,87%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>47,34%</t>
+          <t>47,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
+          <t>68,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>55481</t>
+          <t>54069</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>71160</t>
+          <t>71436</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>51,45%</t>
+          <t>50,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>66,25%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>51371</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>51371</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>51371</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>56462</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>56462</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>56462</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>51371</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>51371</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>51371</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>94974</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>82285</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>109056</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>26,86%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>23,27%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>30,84%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>122</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>81521</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>69786</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>95326</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>70455</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>94864</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>26,27%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>22,49%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>30,72%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>94974</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>82470</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>109319</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>26,86%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>157440</t>
+          <t>159324</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>194637</t>
+          <t>195226</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,4%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>388</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>258662</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>244580</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>271351</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>73,14%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>69,16%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>76,73%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>343</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>228796</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>214991</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>240531</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>215453</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>239862</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>73,73%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>69,28%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>77,51%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>388</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>258662</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>244317</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>271166</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>73,14%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,09%</t>
+          <t>69,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,68%</t>
+          <t>77,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>469316</t>
+          <t>468727</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>506513</t>
+          <t>504629</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>70,69%</t>
+          <t>70,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>76,0%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>532</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>353636</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>353636</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>353636</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>465</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>310317</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>310317</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>310317</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>532</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>353636</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>353636</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>353636</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>31029</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>23321</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>39333</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>25,12%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>18,88%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>31,84%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>36754</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>28679</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>45811</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>28311</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>45895</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>26,91%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>21,0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>33,54%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>31029</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>23883</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>39450</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>25,12%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>56945</t>
+          <t>57901</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>80904</t>
+          <t>79472</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>30,55%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>92513</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>84209</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>100221</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>74,88%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>68,16%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>81,12%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>145</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>99827</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>90770</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>107902</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>90686</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>108270</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>73,09%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>66,46%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>79,0%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>92513</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>84092</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>99659</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>74,88%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,07%</t>
+          <t>66,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>79,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>179219</t>
+          <t>180651</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>203178</t>
+          <t>202222</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>68,9%</t>
+          <t>69,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,11%</t>
+          <t>77,74%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>123542</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>123542</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>123542</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>198</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>136581</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>136581</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>136581</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>123542</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>123542</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>123542</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>147647</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>131055</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>164091</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>27,93%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>24,8%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>31,05%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>210</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>141455</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>124435</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>156383</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>126371</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>157231</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>28,1%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>24,72%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>31,07%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>147647</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>132896</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>166042</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>27,93%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>265693</t>
+          <t>265826</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>313158</t>
+          <t>312670</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>30,3%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>380902</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>364458</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>397494</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>72,07%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>68,95%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>75,2%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>536</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>361904</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>346976</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>378924</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>346128</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>376988</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>71,9%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>68,93%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>75,28%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>570</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>380902</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>362507</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>395653</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>72,07%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,59%</t>
+          <t>68,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,86%</t>
+          <t>74,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>718750</t>
+          <t>719238</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>766215</t>
+          <t>766082</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,65%</t>
+          <t>69,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,25%</t>
+          <t>74,24%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>746</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>503359</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>503359</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>503359</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>792</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2158,7 +2158,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2326,72 +2326,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>22342</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>16073</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>28625</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>35,98%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>25,89%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>46,1%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>19122</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>13551</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>25599</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>13515</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>25249</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>34,46%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>24,42%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>46,14%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>22342</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>16623</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>28903</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>35,98%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>45,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>34256</t>
+          <t>33233</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>50149</t>
+          <t>50168</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>42,67%</t>
         </is>
       </c>
     </row>
@@ -2439,72 +2439,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>39748</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>33465</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>46017</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>64,02%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>53,9%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>74,11%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>36362</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>29885</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>41933</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>30235</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>41969</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>65,54%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>53,86%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>75,58%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>39748</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>33187</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>45467</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>64,02%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>53,45%</t>
+          <t>54,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
+          <t>75,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>67425</t>
+          <t>67406</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>83318</t>
+          <t>84341</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>57,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>71,73%</t>
         </is>
       </c>
     </row>
@@ -2552,57 +2552,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>62090</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>62090</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>62090</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>55484</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>55484</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>55484</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>62090</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>62090</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>62090</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>126269</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>111807</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>142963</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>37,16%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>32,9%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>42,07%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>163</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>115363</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>101869</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>128818</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>101880</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>130422</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>37,87%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>33,44%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>42,28%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>126269</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>111868</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>141566</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>37,16%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>32,92%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>42,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>221254</t>
+          <t>222392</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>259726</t>
+          <t>262186</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>34,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>40,68%</t>
         </is>
       </c>
     </row>
@@ -2782,74 +2782,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>213524</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>196830</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>227986</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>62,84%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>57,93%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>67,1%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>278</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>189290</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>175835</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>202784</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>174231</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>202773</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>62,13%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>57,72%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>57,19%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>66,56%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>308</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>213524</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>198227</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>227925</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>62,84%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>58,34%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>67,08%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>586</t>
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>384720</t>
+          <t>382260</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>423192</t>
+          <t>422054</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,7%</t>
+          <t>59,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,67%</t>
+          <t>65,49%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>487</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>339793</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>339793</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>339793</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>441</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>304653</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>304653</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>304653</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>487</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>339793</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>339793</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>339793</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>57530</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>48734</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>67093</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>42,02%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>35,6%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>49,01%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>46922</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>38085</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>55448</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>38617</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>56182</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>40,16%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>32,6%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>47,46%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>57530</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>46724</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>66757</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>42,02%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,76%</t>
+          <t>48,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>92287</t>
+          <t>91839</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>118275</t>
+          <t>117906</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,62%</t>
+          <t>46,47%</t>
         </is>
       </c>
     </row>
@@ -3125,72 +3125,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>79368</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>69805</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>88164</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>57,98%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>50,99%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>64,4%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>69905</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>61379</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>78742</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>60645</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>78210</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>59,84%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>52,54%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>67,4%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>79368</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>70141</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>90174</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>57,98%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>51,24%</t>
+          <t>51,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>65,87%</t>
+          <t>66,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>135450</t>
+          <t>135819</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>161438</t>
+          <t>161886</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>53,38%</t>
+          <t>53,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>63,63%</t>
+          <t>63,8%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>136898</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>136898</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>136898</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>166</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>116827</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>116827</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>116827</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>193</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>136898</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>136898</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>136898</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>293</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>206142</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>188165</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>225055</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>38,26%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>34,92%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>41,77%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>256</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>181408</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>164635</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>199800</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>164366</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>199035</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>38,03%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>34,52%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>41,89%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>293</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>206142</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>189494</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>224900</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>38,26%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>41,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>360875</t>
+          <t>363763</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>412380</t>
+          <t>411236</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>40,49%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>476</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>332639</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>313726</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>350616</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>61,74%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>58,23%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>65,08%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>431</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>295557</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>277165</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>312330</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>277930</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>312599</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>61,97%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>58,11%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>65,48%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>476</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>332639</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>313881</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>349287</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>61,74%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>58,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,83%</t>
+          <t>65,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>603366</t>
+          <t>604510</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>654871</t>
+          <t>651983</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>59,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>64,47%</t>
+          <t>64,19%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>769</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>687</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>476965</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>476965</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>476965</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>769</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3761,7 +3761,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3929,72 +3929,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>20814</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>14947</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>26501</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>40,62%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>29,17%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>51,72%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>12298</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>8343</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>17183</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>7872</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>17703</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>30,26%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>20,53%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>42,28%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>20814</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>15513</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>27249</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>40,62%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>53,18%</t>
+          <t>43,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26764</t>
+          <t>25921</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>40797</t>
+          <t>40445</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>44,02%</t>
         </is>
       </c>
     </row>
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>30423</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>24736</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>36290</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>59,38%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>48,28%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>70,83%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>28343</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>23458</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>32298</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>22938</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>32769</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>69,74%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>57,72%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>79,47%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>30423</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>23988</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>35724</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>59,38%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>56,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,72%</t>
+          <t>80,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>51081</t>
+          <t>51433</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>65114</t>
+          <t>65957</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>55,6%</t>
+          <t>55,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>70,87%</t>
+          <t>71,79%</t>
         </is>
       </c>
     </row>
@@ -4155,57 +4155,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>51237</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>51237</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>51237</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>40641</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>40641</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>40641</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>51237</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>51237</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>51237</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4272,72 +4272,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>132938</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>118813</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>147886</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>35,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>31,28%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>38,93%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>181</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>118753</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>104818</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>134055</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>105387</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>134675</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>34,17%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>30,16%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>38,57%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>132938</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>118404</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>147544</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>35,0%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,84%</t>
+          <t>38,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>229369</t>
+          <t>230704</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>270805</t>
+          <t>272918</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>37,52%</t>
         </is>
       </c>
     </row>
@@ -4385,72 +4385,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>246928</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>231980</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>261053</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>65,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>61,07%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>68,72%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>343</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>228802</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>213500</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>242737</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>212880</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>242168</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>65,83%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>61,43%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>69,84%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>349</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>246928</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>232322</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>261462</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>65,0%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,16%</t>
+          <t>61,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,83%</t>
+          <t>69,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>456616</t>
+          <t>454503</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>498052</t>
+          <t>496717</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,77%</t>
+          <t>62,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,47%</t>
+          <t>68,28%</t>
         </is>
       </c>
     </row>
@@ -4498,57 +4498,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>544</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>379866</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>379866</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>379866</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>524</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>347555</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>347555</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>347555</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>544</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>379866</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>379866</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>379866</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4615,72 +4615,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>59642</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>50969</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>69527</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>42,62%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>36,42%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>49,69%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>52411</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>43396</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>61433</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>43049</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>61462</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>38,53%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>31,9%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>45,16%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>59642</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>49483</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>68632</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>42,62%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>49,05%</t>
+          <t>45,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>98131</t>
+          <t>99088</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>125227</t>
+          <t>125749</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>35,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>45,57%</t>
         </is>
       </c>
     </row>
@@ -4728,72 +4728,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>80288</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>70403</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>88961</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>57,38%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>50,31%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>63,58%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>124</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>83616</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>74594</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>92631</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>74565</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>92978</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>61,47%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>54,84%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>68,1%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>80288</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>71298</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>90447</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>57,38%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>50,95%</t>
+          <t>54,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>68,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>150730</t>
+          <t>150208</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>177826</t>
+          <t>176869</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>54,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>64,44%</t>
+          <t>64,09%</t>
         </is>
       </c>
     </row>
@@ -4841,57 +4841,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>139930</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>139930</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>139930</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>202</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>136027</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>136027</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>136027</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>139930</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>139930</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>139930</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4958,74 +4958,74 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>314</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>213394</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>195913</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>233758</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>37,37%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>34,31%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>40,94%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>277</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>183462</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>166664</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>201612</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>165689</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>201641</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>35,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>31,79%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>31,61%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>38,46%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>314</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>213394</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>196243</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>232148</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>37,37%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>34,37%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>40,65%</t>
-        </is>
-      </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>591</t>
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>371768</t>
+          <t>372034</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>424218</t>
+          <t>420792</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>38,42%</t>
         </is>
       </c>
     </row>
@@ -5071,72 +5071,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>357639</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>337275</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>375120</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>62,63%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>59,06%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>65,69%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>512</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>340761</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>322611</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>357559</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>322582</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>358534</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>65,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>61,54%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>68,21%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>357639</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>338885</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>374790</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>62,63%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>59,35%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,63%</t>
+          <t>68,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>671038</t>
+          <t>674464</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>723488</t>
+          <t>723222</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,27%</t>
+          <t>61,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,06%</t>
+          <t>66,03%</t>
         </is>
       </c>
     </row>
@@ -5184,57 +5184,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>825</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>789</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>524223</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>524223</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>524223</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>825</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5364,7 +5364,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5532,72 +5532,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>13530</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8356</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>19891</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>23,85%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>14,73%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>35,06%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>7546</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3798</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>13140</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>13,8%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>6,95%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>24,03%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>14842</t>
+          <t>8305</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9383</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21389</t>
+          <t>13779</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>22388</t>
+          <t>21835</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15538</t>
+          <t>15312</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>31007</t>
+          <t>30047</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>29,03%</t>
         </is>
       </c>
     </row>
@@ -5645,72 +5645,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>43202</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>36841</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>48376</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>76,15%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>64,94%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>85,27%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>47132</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>41538</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>50880</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>86,2%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>75,97%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>93,05%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>47162</t>
+          <t>38453</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>40615</t>
+          <t>32979</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>52621</t>
+          <t>41997</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,5%</t>
+          <t>70,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>94294</t>
+          <t>81655</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>85675</t>
+          <t>73443</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>101144</t>
+          <t>88178</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>80,81%</t>
+          <t>78,9%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,43%</t>
+          <t>70,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>85,2%</t>
         </is>
       </c>
     </row>
@@ -5758,57 +5758,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5875,72 +5875,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>76316</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>62351</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>91745</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>16,04%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>13,11%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>19,29%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>112</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>103515</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>76840</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>178132</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>22,48%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>16,69%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>38,68%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>81271</t>
+          <t>77128</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>66551</t>
+          <t>63971</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>96974</t>
+          <t>91917</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>184786</t>
+          <t>153443</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>155181</t>
+          <t>133640</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>265359</t>
+          <t>177191</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>19,51%</t>
         </is>
       </c>
     </row>
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>546</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>399362</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>383933</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>413327</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>83,96%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>80,71%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>86,89%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>531</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>356995</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>282378</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>383670</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>77,52%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>61,32%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>83,31%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>546</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>435348</t>
+          <t>355320</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>419645</t>
+          <t>340531</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>450068</t>
+          <t>368477</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>82,16%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,23%</t>
+          <t>78,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>85,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>792343</t>
+          <t>754683</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>711770</t>
+          <t>730935</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>821948</t>
+          <t>774486</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>83,1%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>85,28%</t>
         </is>
       </c>
     </row>
@@ -6101,57 +6101,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>643</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>460510</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>460510</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>460510</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>432448</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>432448</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>432448</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>977129</t>
+          <t>908126</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>977129</t>
+          <t>908126</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>977129</t>
+          <t>908126</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>30009</t>
+          <t>31698</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22823</t>
+          <t>23220</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39053</t>
+          <t>41312</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>34104</t>
+          <t>30199</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25239</t>
+          <t>21956</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44383</t>
+          <t>39080</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>64114</t>
+          <t>61897</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>50942</t>
+          <t>51237</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>77171</t>
+          <t>74590</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,5%</t>
         </is>
       </c>
     </row>
@@ -6331,72 +6331,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>135764</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>126150</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>144242</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>81,07%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>75,33%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>86,13%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>119542</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>110498</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>126728</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>79,93%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>73,89%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>84,74%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>148301</t>
+          <t>119777</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>138022</t>
+          <t>110896</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>157166</t>
+          <t>128020</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>81,3%</t>
+          <t>79,86%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>73,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>267843</t>
+          <t>255541</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>254786</t>
+          <t>242848</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>281015</t>
+          <t>266201</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>80,5%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>76,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,65%</t>
+          <t>83,86%</t>
         </is>
       </c>
     </row>
@@ -6444,57 +6444,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>167462</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>167462</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>167462</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>182405</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>182405</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>182405</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>331957</t>
+          <t>317438</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>331957</t>
+          <t>317438</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>331957</t>
+          <t>317438</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6561,72 +6561,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>121544</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>105481</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>140487</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>17,37%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>15,07%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>20,07%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>168</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>141069</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>111726</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>213673</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>21,22%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>16,81%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>32,14%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>130218</t>
+          <t>115631</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>110621</t>
+          <t>100715</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>151459</t>
+          <t>134229</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>271288</t>
+          <t>237175</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>237586</t>
+          <t>214098</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>342996</t>
+          <t>263885</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>19,86%</t>
         </is>
       </c>
     </row>
@@ -6674,72 +6674,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>804</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>578328</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>559385</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>594391</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>82,63%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>79,93%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>84,93%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>774</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>523669</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>451065</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>553012</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>78,78%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>67,86%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>83,19%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>804</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>630810</t>
+          <t>513551</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>609569</t>
+          <t>494953</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>650407</t>
+          <t>528467</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>81,62%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,1%</t>
+          <t>78,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>83,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1154479</t>
+          <t>1091879</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1082771</t>
+          <t>1065169</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1188181</t>
+          <t>1114956</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>82,15%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>80,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>83,89%</t>
         </is>
       </c>
     </row>
@@ -6787,57 +6787,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>699872</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>699872</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>699872</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>942</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>664738</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>664738</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>664738</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>976</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>761028</t>
+          <t>629182</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>761028</t>
+          <t>629182</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>761028</t>
+          <t>629182</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1425767</t>
+          <t>1329054</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1425767</t>
+          <t>1329054</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1425767</t>
+          <t>1329054</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
